--- a/data/spain/p4_modeling/2024-10-13/df_best_model.xlsx
+++ b/data/spain/p4_modeling/2024-10-13/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,55 +486,65 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>odd_weight</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_sup_cap</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>X_shape_missing</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>model_name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>% roi_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t># result 1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t># result 0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t># result 2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t># pred 1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t># pred 0</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t># pred 2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t># aciertos</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
@@ -542,25 +552,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B2" t="n">
-        <v>3.399615627898761</v>
+        <v>12.10718475747765</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.07543079560311952</v>
+        <v>1.400969678484506</v>
       </c>
       <c r="D2" t="n">
-        <v>4.799946410829033</v>
+        <v>11.692056109916</v>
       </c>
       <c r="E2" t="n">
-        <v>10.04168471940596</v>
+        <v>9.06231977880908</v>
       </c>
       <c r="F2" t="n">
-        <v>2008.336943881192</v>
+        <v>2444.689815832917</v>
       </c>
       <c r="G2" t="n">
-        <v>10.04168471940596</v>
+        <v>11.75331642227364</v>
       </c>
       <c r="H2" t="n">
         <v>-0.5</v>
@@ -570,74 +580,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>(200, 72)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>134.1244704383136</v>
-      </c>
-      <c r="P2" t="n">
-        <v>87</v>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>(208, 37)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>7.389415276273319</v>
       </c>
       <c r="R2" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S2" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="T2" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="U2" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="V2" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="W2" t="n">
-        <v>56.99999999999999</v>
+        <v>52</v>
+      </c>
+      <c r="X2" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>57.21153846153846</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>322</v>
+        <v>545</v>
       </c>
       <c r="B3" t="n">
-        <v>12.47340784862854</v>
+        <v>8.605302916440969</v>
       </c>
       <c r="C3" t="n">
-        <v>1.284046840270327</v>
+        <v>1.103648868968158</v>
       </c>
       <c r="D3" t="n">
-        <v>11.79093959363173</v>
+        <v>3.145398781218162</v>
       </c>
       <c r="E3" t="n">
-        <v>9.747224470876645</v>
+        <v>7.485829429279255</v>
       </c>
       <c r="F3" t="n">
-        <v>1949.444894175329</v>
+        <v>1826.006982301658</v>
       </c>
       <c r="G3" t="n">
-        <v>9.747224470876645</v>
+        <v>8.778879722604124</v>
       </c>
       <c r="H3" t="n">
         <v>-0.5</v>
@@ -647,151 +667,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>40</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>(200, 37)</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>(208, 24)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>6.591019396788196</v>
-      </c>
-      <c r="P3" t="n">
-        <v>87</v>
-      </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>6.954413735603987</v>
       </c>
       <c r="R3" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S3" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="T3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="U3" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="V3" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="W3" t="n">
-        <v>56.99999999999999</v>
+        <v>65</v>
+      </c>
+      <c r="X3" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>527</v>
+        <v>257</v>
       </c>
       <c r="B4" t="n">
-        <v>13.97745520877321</v>
+        <v>22.57972645092249</v>
       </c>
       <c r="C4" t="n">
-        <v>4.001190749707932</v>
+        <v>2.641911195978608</v>
       </c>
       <c r="D4" t="n">
-        <v>12.2593612634358</v>
+        <v>9.845656187790773</v>
       </c>
       <c r="E4" t="n">
-        <v>7.04837908391614</v>
+        <v>3.996712992067087</v>
       </c>
       <c r="F4" t="n">
-        <v>1409.675816783228</v>
+        <v>1786.134508699619</v>
       </c>
       <c r="G4" t="n">
-        <v>7.04837908391614</v>
+        <v>8.587185137978937</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>(208, 37)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>0.7615703736270604</v>
-      </c>
-      <c r="P4" t="n">
-        <v>87</v>
-      </c>
       <c r="Q4" t="n">
+        <v>2.250368578266348</v>
+      </c>
+      <c r="R4" t="n">
+        <v>92</v>
+      </c>
+      <c r="S4" t="n">
+        <v>52</v>
+      </c>
+      <c r="T4" t="n">
+        <v>64</v>
+      </c>
+      <c r="U4" t="n">
+        <v>91</v>
+      </c>
+      <c r="V4" t="n">
         <v>50</v>
       </c>
-      <c r="R4" t="n">
-        <v>63</v>
-      </c>
-      <c r="S4" t="n">
-        <v>94</v>
-      </c>
-      <c r="T4" t="n">
-        <v>34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>72</v>
-      </c>
-      <c r="V4" t="n">
-        <v>114</v>
-      </c>
       <c r="W4" t="n">
-        <v>56.99999999999999</v>
+        <v>67</v>
+      </c>
+      <c r="X4" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>57.69230769230769</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>545</v>
+        <v>342</v>
       </c>
       <c r="B5" t="n">
-        <v>6.410206570329883</v>
+        <v>3.491552382499207</v>
       </c>
       <c r="C5" t="n">
-        <v>1.013867492746431</v>
+        <v>-0.04383488764631878</v>
       </c>
       <c r="D5" t="n">
-        <v>3.454327690067232</v>
+        <v>5.234157978699358</v>
       </c>
       <c r="E5" t="n">
-        <v>5.753896331524535</v>
+        <v>10.91038646363221</v>
       </c>
       <c r="F5" t="n">
-        <v>1150.779266304907</v>
+        <v>1531.657695051108</v>
       </c>
       <c r="G5" t="n">
-        <v>5.753896331524535</v>
+        <v>7.363738918514944</v>
       </c>
       <c r="H5" t="n">
         <v>-0.5</v>
@@ -801,844 +841,954 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>(200, 24)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>4.675195597738321</v>
-      </c>
-      <c r="P5" t="n">
-        <v>87</v>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>(208, 72)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>168.9880869760446</v>
       </c>
       <c r="R5" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S5" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="T5" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="U5" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="V5" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="W5" t="n">
-        <v>55.50000000000001</v>
+        <v>48</v>
+      </c>
+      <c r="X5" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="B6" t="n">
-        <v>7.178257475463812</v>
+        <v>8.428306452845128</v>
       </c>
       <c r="C6" t="n">
-        <v>4.761098090642642</v>
+        <v>1.222147179791819</v>
       </c>
       <c r="D6" t="n">
-        <v>9.292299404559715</v>
+        <v>10.37340856807602</v>
       </c>
       <c r="E6" t="n">
-        <v>5.207677831109552</v>
+        <v>4.276012208017388</v>
       </c>
       <c r="F6" t="n">
-        <v>1041.53556622191</v>
+        <v>1378.769757809465</v>
       </c>
       <c r="G6" t="n">
-        <v>5.207677831109552</v>
+        <v>6.628700758699351</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>30</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>(200, 10)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>(208, 55)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>0.09379763490792342</v>
-      </c>
-      <c r="P6" t="n">
-        <v>87</v>
-      </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>4.423815452266957</v>
       </c>
       <c r="R6" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S6" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="T6" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="U6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V6" t="n">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="W6" t="n">
-        <v>57.49999999999999</v>
+        <v>78</v>
+      </c>
+      <c r="X6" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>57.69230769230769</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="B7" t="n">
-        <v>8.752684093422506</v>
+        <v>9.054109062002366</v>
       </c>
       <c r="C7" t="n">
-        <v>1.398872440244002</v>
+        <v>2.742707624764639</v>
       </c>
       <c r="D7" t="n">
-        <v>11.17237767973668</v>
+        <v>4.824698764551876</v>
       </c>
       <c r="E7" t="n">
-        <v>4.649342929886346</v>
+        <v>3.616627140479269</v>
       </c>
       <c r="F7" t="n">
-        <v>929.8685859772692</v>
+        <v>1311.410530205432</v>
       </c>
       <c r="G7" t="n">
-        <v>4.649342929886346</v>
+        <v>6.304858318295345</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>30</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>(200, 55)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>(208, 15)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>2.323636091561981</v>
-      </c>
-      <c r="P7" t="n">
-        <v>87</v>
-      </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>1.298771572065172</v>
       </c>
       <c r="R7" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S7" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="T7" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="U7" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="V7" t="n">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="W7" t="n">
-        <v>56.99999999999999</v>
+        <v>60</v>
+      </c>
+      <c r="X7" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>56.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>257</v>
+        <v>527</v>
       </c>
       <c r="B8" t="n">
-        <v>13.1353381867865</v>
+        <v>14.15591699316498</v>
       </c>
       <c r="C8" t="n">
-        <v>1.940979547623627</v>
+        <v>4.137113402242927</v>
       </c>
       <c r="D8" t="n">
-        <v>10.1396260227405</v>
+        <v>13.14472661527103</v>
       </c>
       <c r="E8" t="n">
-        <v>3.964062102346186</v>
+        <v>7.508625849042001</v>
       </c>
       <c r="F8" t="n">
-        <v>792.8124204692372</v>
+        <v>1248.248720042126</v>
       </c>
       <c r="G8" t="n">
-        <v>3.964062102346186</v>
+        <v>6.001195769433296</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>(200, 37)</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O8" t="n">
-        <v>1.042299779613573</v>
-      </c>
-      <c r="P8" t="n">
-        <v>87</v>
-      </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>0.4505756033131121</v>
       </c>
       <c r="R8" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S8" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="T8" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="V8" t="n">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="W8" t="n">
-        <v>56.99999999999999</v>
+        <v>73</v>
+      </c>
+      <c r="X8" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="B9" t="n">
-        <v>17.67122624241809</v>
+        <v>0.9352969240871858</v>
       </c>
       <c r="C9" t="n">
-        <v>0.977984113872236</v>
+        <v>0.04451478784717239</v>
       </c>
       <c r="D9" t="n">
-        <v>2.882743357033008</v>
+        <v>7.431311288717917</v>
       </c>
       <c r="E9" t="n">
-        <v>3.798629200019412</v>
+        <v>3.016561755729537</v>
       </c>
       <c r="F9" t="n">
-        <v>759.7258400038824</v>
+        <v>1121.884456545473</v>
       </c>
       <c r="G9" t="n">
-        <v>3.798629200019412</v>
+        <v>5.393675271853236</v>
       </c>
       <c r="H9" t="n">
         <v>-0.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>30</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>(200, 34)</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>(208, 15)</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>2.884142028625698</v>
-      </c>
-      <c r="P9" t="n">
-        <v>87</v>
-      </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>120.1659210950468</v>
       </c>
       <c r="R9" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S9" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="T9" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="U9" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="V9" t="n">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="W9" t="n">
-        <v>56.99999999999999</v>
+        <v>51</v>
+      </c>
+      <c r="X9" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>56.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>496</v>
+        <v>263</v>
       </c>
       <c r="B10" t="n">
-        <v>2.283904304179657</v>
+        <v>8.089405764259022</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5115983132979796</v>
+        <v>2.118053814160624</v>
       </c>
       <c r="D10" t="n">
-        <v>3.753636412988089</v>
+        <v>4.959631456368085</v>
       </c>
       <c r="E10" t="n">
-        <v>3.794328654183682</v>
+        <v>1.703212293646249</v>
       </c>
       <c r="F10" t="n">
-        <v>758.8657308367365</v>
+        <v>865.8048062551555</v>
       </c>
       <c r="G10" t="n">
-        <v>3.794328654183682</v>
+        <v>4.16252310699594</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>(200, 63)</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>6.416616817447719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>87</v>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>(208, 61)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q10" t="n">
+        <v>0.965258426942061</v>
+      </c>
+      <c r="R10" t="n">
+        <v>92</v>
+      </c>
+      <c r="S10" t="n">
+        <v>52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>64</v>
+      </c>
+      <c r="U10" t="n">
+        <v>100</v>
+      </c>
+      <c r="V10" t="n">
         <v>50</v>
       </c>
-      <c r="R10" t="n">
-        <v>63</v>
-      </c>
-      <c r="S10" t="n">
-        <v>96</v>
-      </c>
-      <c r="T10" t="n">
-        <v>44</v>
-      </c>
-      <c r="U10" t="n">
-        <v>60</v>
-      </c>
-      <c r="V10" t="n">
-        <v>110</v>
-      </c>
       <c r="W10" t="n">
-        <v>55.00000000000001</v>
+        <v>58</v>
+      </c>
+      <c r="X10" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>332</v>
+        <v>496</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8320688097994343</v>
+        <v>2.283904304179657</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3263278327631349</v>
+        <v>0.5417075806368785</v>
       </c>
       <c r="D11" t="n">
-        <v>4.391121324649786</v>
+        <v>3.921089594895539</v>
       </c>
       <c r="E11" t="n">
-        <v>3.575645821812714</v>
+        <v>3.878552301262476</v>
       </c>
       <c r="F11" t="n">
-        <v>715.1291643625427</v>
+        <v>848.9057027011186</v>
       </c>
       <c r="G11" t="n">
-        <v>3.575645821812714</v>
+        <v>4.081277416832301</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>9.957219896128496</v>
-      </c>
-      <c r="P11" t="n">
-        <v>87</v>
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>(208, 63)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>6.534096923720352</v>
       </c>
       <c r="R11" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S11" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="T11" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="U11" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="V11" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="W11" t="n">
-        <v>57.99999999999999</v>
+        <v>60</v>
+      </c>
+      <c r="X11" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>55.28846153846154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>201</v>
+        <v>332</v>
       </c>
       <c r="B12" t="n">
-        <v>8.097641543874287</v>
+        <v>1.326241201308739</v>
       </c>
       <c r="C12" t="n">
-        <v>2.464193769935023</v>
+        <v>0.1673665936641422</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5249942123104</v>
+        <v>3.827986159422393</v>
       </c>
       <c r="E12" t="n">
-        <v>3.566893063281421</v>
+        <v>2.97041690049046</v>
       </c>
       <c r="F12" t="n">
-        <v>713.3786126562843</v>
+        <v>815.4317084531527</v>
       </c>
       <c r="G12" t="n">
-        <v>3.566893063281421</v>
+        <v>3.920344752178619</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>(200, 15)</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>0.4474888731560563</v>
-      </c>
-      <c r="P12" t="n">
-        <v>87</v>
-      </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>22.42369923621468</v>
       </c>
       <c r="R12" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S12" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="T12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="U12" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="V12" t="n">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="W12" t="n">
-        <v>55.50000000000001</v>
+        <v>61</v>
+      </c>
+      <c r="X12" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>58.17307692307693</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>563</v>
+        <v>214</v>
       </c>
       <c r="B13" t="n">
-        <v>6.512648594112931</v>
+        <v>9.628241082021564</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3854486688020779</v>
+        <v>1.076819137851159</v>
       </c>
       <c r="D13" t="n">
-        <v>3.693661721289414</v>
+        <v>2.6156873884928</v>
       </c>
       <c r="E13" t="n">
-        <v>3.087334031916351</v>
+        <v>4.123499739187864</v>
       </c>
       <c r="F13" t="n">
-        <v>617.4668063832702</v>
+        <v>776.7187344598703</v>
       </c>
       <c r="G13" t="n">
-        <v>3.087334031916351</v>
+        <v>3.734224684903223</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>30</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>(200, 11)</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>(208, 34)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>7.009715123706007</v>
-      </c>
-      <c r="P13" t="n">
-        <v>87</v>
-      </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>2.467829047276255</v>
       </c>
       <c r="R13" t="n">
+        <v>92</v>
+      </c>
+      <c r="S13" t="n">
+        <v>52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>64</v>
+      </c>
+      <c r="U13" t="n">
+        <v>102</v>
+      </c>
+      <c r="V13" t="n">
+        <v>43</v>
+      </c>
+      <c r="W13" t="n">
         <v>63</v>
       </c>
-      <c r="S13" t="n">
-        <v>93</v>
-      </c>
-      <c r="T13" t="n">
-        <v>50</v>
-      </c>
-      <c r="U13" t="n">
-        <v>57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>114</v>
-      </c>
-      <c r="W13" t="n">
-        <v>56.99999999999999</v>
+      <c r="X13" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>211</v>
+        <v>563</v>
       </c>
       <c r="B14" t="n">
-        <v>2.35927466711454</v>
+        <v>7.462564419815733</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4983533138840091</v>
+        <v>0.5313687552276468</v>
       </c>
       <c r="D14" t="n">
-        <v>4.804156384815718</v>
+        <v>4.499539220489662</v>
       </c>
       <c r="E14" t="n">
-        <v>3.033594357888973</v>
+        <v>3.96128713902109</v>
       </c>
       <c r="F14" t="n">
-        <v>606.7188715777945</v>
+        <v>686.0610400663761</v>
       </c>
       <c r="G14" t="n">
-        <v>3.033594357888973</v>
+        <v>3.298370384934501</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>30</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>(200, 10)</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>(208, 11)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O14" t="n">
-        <v>5.087236250615235</v>
-      </c>
-      <c r="P14" t="n">
-        <v>87</v>
-      </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>5.20730961782167</v>
       </c>
       <c r="R14" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S14" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="T14" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U14" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="V14" t="n">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="W14" t="n">
-        <v>56.00000000000001</v>
+        <v>58</v>
+      </c>
+      <c r="X14" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>275</v>
+        <v>585</v>
       </c>
       <c r="B15" t="n">
-        <v>1.873791594607724</v>
+        <v>2.231052437064881</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1908792159234744</v>
+        <v>0.5386582417874473</v>
       </c>
       <c r="D15" t="n">
-        <v>6.675450613282297</v>
+        <v>1.747016046841029</v>
       </c>
       <c r="E15" t="n">
-        <v>2.962371840823204</v>
+        <v>1.607772690481254</v>
       </c>
       <c r="F15" t="n">
-        <v>592.4743681646407</v>
+        <v>638.6667393816132</v>
       </c>
       <c r="G15" t="n">
-        <v>2.962371840823204</v>
+        <v>3.07051317010391</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>30</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>(200, 15)</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>14.51961446662088</v>
-      </c>
-      <c r="P15" t="n">
-        <v>87</v>
-      </c>
       <c r="Q15" t="n">
-        <v>50</v>
+        <v>4.700299247097613</v>
       </c>
       <c r="R15" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S15" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="T15" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U15" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="V15" t="n">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="W15" t="n">
-        <v>55.50000000000001</v>
+        <v>64</v>
+      </c>
+      <c r="X15" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>57.69230769230769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="B16" t="n">
-        <v>3.207567586131562</v>
+        <v>0.9910041724287646</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7104043314008581</v>
+        <v>0.3611942251978877</v>
       </c>
       <c r="D16" t="n">
-        <v>3.866318159289967</v>
+        <v>3.282317867417478</v>
       </c>
       <c r="E16" t="n">
-        <v>2.871374035917596</v>
+        <v>3.137735576463335</v>
       </c>
       <c r="F16" t="n">
-        <v>574.2748071835192</v>
+        <v>567.935058686722</v>
       </c>
       <c r="G16" t="n">
-        <v>2.871374035917596</v>
+        <v>2.730457012916932</v>
       </c>
       <c r="H16" t="n">
         <v>-0.5</v>
@@ -1648,74 +1798,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>30</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>(200, 10)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>(208, 10)</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O16" t="n">
-        <v>3.041887005749931</v>
-      </c>
-      <c r="P16" t="n">
-        <v>87</v>
-      </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>6.559525658033418</v>
       </c>
       <c r="R16" t="n">
+        <v>92</v>
+      </c>
+      <c r="S16" t="n">
+        <v>52</v>
+      </c>
+      <c r="T16" t="n">
+        <v>64</v>
+      </c>
+      <c r="U16" t="n">
+        <v>92</v>
+      </c>
+      <c r="V16" t="n">
         <v>63</v>
       </c>
-      <c r="S16" t="n">
-        <v>87</v>
-      </c>
-      <c r="T16" t="n">
-        <v>61</v>
-      </c>
-      <c r="U16" t="n">
-        <v>52</v>
-      </c>
-      <c r="V16" t="n">
-        <v>112</v>
-      </c>
       <c r="W16" t="n">
-        <v>56.00000000000001</v>
+        <v>53</v>
+      </c>
+      <c r="X16" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>43</v>
+        <v>235</v>
       </c>
       <c r="B17" t="n">
-        <v>8.675079640459053</v>
+        <v>2.560497571928922</v>
       </c>
       <c r="C17" t="n">
-        <v>1.504885647744971</v>
+        <v>0.7681349946589355</v>
       </c>
       <c r="D17" t="n">
-        <v>2.663304258538262</v>
+        <v>3.33755089608516</v>
       </c>
       <c r="E17" t="n">
-        <v>2.266455847914335</v>
+        <v>2.770525465884343</v>
       </c>
       <c r="F17" t="n">
-        <v>453.291169582867</v>
+        <v>489.8362855182945</v>
       </c>
       <c r="G17" t="n">
-        <v>2.266455847914335</v>
+        <v>2.354982141914877</v>
       </c>
       <c r="H17" t="n">
         <v>-0.5</v>
@@ -1725,74 +1885,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>30</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>(200, 34)</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>(208, 10)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>0.5060651626989435</v>
-      </c>
-      <c r="P17" t="n">
-        <v>87</v>
-      </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>2.065844100698117</v>
       </c>
       <c r="R17" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S17" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="T17" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="V17" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="W17" t="n">
-        <v>55.00000000000001</v>
+        <v>54</v>
+      </c>
+      <c r="X17" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>291</v>
+        <v>378</v>
       </c>
       <c r="B18" t="n">
-        <v>2.909317089980574</v>
+        <v>4.234413552461714</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.09291884580094489</v>
+        <v>1.789306997647699</v>
       </c>
       <c r="D18" t="n">
-        <v>2.238069296361617</v>
+        <v>1.567594379399676</v>
       </c>
       <c r="E18" t="n">
-        <v>1.843397142100094</v>
+        <v>1.081504011572696</v>
       </c>
       <c r="F18" t="n">
-        <v>368.6794284200188</v>
+        <v>447.1681013801792</v>
       </c>
       <c r="G18" t="n">
-        <v>1.843397142100094</v>
+        <v>2.149846641250861</v>
       </c>
       <c r="H18" t="n">
         <v>-0.25</v>
@@ -1802,305 +1972,345 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>25</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>(208, 38)</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O18" t="n">
-        <v>20.83878648308983</v>
-      </c>
-      <c r="P18" t="n">
-        <v>87</v>
-      </c>
       <c r="Q18" t="n">
-        <v>50</v>
+        <v>0.2014968052308201</v>
       </c>
       <c r="R18" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="T18" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="U18" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="V18" t="n">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="W18" t="n">
-        <v>56.49999999999999</v>
+        <v>77</v>
+      </c>
+      <c r="X18" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>54.80769230769231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>620</v>
+        <v>291</v>
       </c>
       <c r="B19" t="n">
-        <v>6.158584080634737</v>
+        <v>3.018872452130487</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8891757421521669</v>
+        <v>-0.1099105091417574</v>
       </c>
       <c r="D19" t="n">
-        <v>3.363485481852411</v>
+        <v>2.304412591176481</v>
       </c>
       <c r="E19" t="n">
-        <v>1.606432664284257</v>
+        <v>1.776827103888171</v>
       </c>
       <c r="F19" t="n">
-        <v>321.2865328568515</v>
+        <v>443.954963276892</v>
       </c>
       <c r="G19" t="n">
-        <v>1.606432664284257</v>
+        <v>2.134398861908135</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>25</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>0.8066537222394717</v>
-      </c>
-      <c r="P19" t="n">
-        <v>87</v>
-      </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>20.41942475359919</v>
       </c>
       <c r="R19" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S19" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="T19" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="U19" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="V19" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="W19" t="n">
-        <v>56.99999999999999</v>
+        <v>72</v>
+      </c>
+      <c r="X19" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="B20" t="n">
-        <v>1.224707616973789</v>
+        <v>4.65528666383893</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1451942940472342</v>
+        <v>2.08504556436374</v>
       </c>
       <c r="D20" t="n">
-        <v>0.661981275665429</v>
+        <v>2.726386485675066</v>
       </c>
       <c r="E20" t="n">
-        <v>1.54543642491625</v>
+        <v>2.302640145264584</v>
       </c>
       <c r="F20" t="n">
-        <v>309.08728498325</v>
+        <v>440.7521299946549</v>
       </c>
       <c r="G20" t="n">
-        <v>1.54543642491625</v>
+        <v>2.119000624974302</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>(200, 19)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>11.64391982520672</v>
-      </c>
-      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>(208, 12)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.01628504488865863</v>
+      </c>
+      <c r="R20" t="n">
+        <v>92</v>
+      </c>
+      <c r="S20" t="n">
+        <v>52</v>
+      </c>
+      <c r="T20" t="n">
+        <v>64</v>
+      </c>
+      <c r="U20" t="n">
         <v>87</v>
       </c>
-      <c r="Q20" t="n">
-        <v>50</v>
-      </c>
-      <c r="R20" t="n">
-        <v>63</v>
-      </c>
-      <c r="S20" t="n">
-        <v>113</v>
-      </c>
-      <c r="T20" t="n">
-        <v>34</v>
-      </c>
-      <c r="U20" t="n">
-        <v>53</v>
-      </c>
       <c r="V20" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="W20" t="n">
-        <v>56.99999999999999</v>
+        <v>84</v>
+      </c>
+      <c r="X20" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>51.92307692307693</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>585</v>
+        <v>364</v>
       </c>
       <c r="B21" t="n">
-        <v>1.984356366640399</v>
+        <v>3.554857258968642</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6859422988572202</v>
+        <v>0.2030952032102284</v>
       </c>
       <c r="D21" t="n">
-        <v>1.510043695580055</v>
+        <v>2.405362694277401</v>
       </c>
       <c r="E21" t="n">
-        <v>1.51648541394287</v>
+        <v>1.673273056322793</v>
       </c>
       <c r="F21" t="n">
-        <v>303.297082788574</v>
+        <v>392.0680380950761</v>
       </c>
       <c r="G21" t="n">
-        <v>1.51648541394287</v>
+        <v>1.884942490841712</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>(208, 14)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O21" t="n">
-        <v>1.210806093266641</v>
-      </c>
-      <c r="P21" t="n">
-        <v>87</v>
-      </c>
       <c r="Q21" t="n">
-        <v>50</v>
+        <v>8.281078336894867</v>
       </c>
       <c r="R21" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S21" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="T21" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="U21" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="V21" t="n">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="W21" t="n">
-        <v>56.99999999999999</v>
+        <v>73</v>
+      </c>
+      <c r="X21" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>56.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B22" t="n">
-        <v>4.718924656410942</v>
+        <v>5.846436958896369</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2893180168917761</v>
+        <v>0.2327398340944661</v>
       </c>
       <c r="D22" t="n">
-        <v>2.506983824783023</v>
+        <v>2.725242455450207</v>
       </c>
       <c r="E22" t="n">
-        <v>1.431811348748618</v>
+        <v>0.9613065739555248</v>
       </c>
       <c r="F22" t="n">
-        <v>286.3622697497237</v>
+        <v>373.8829841170939</v>
       </c>
       <c r="G22" t="n">
-        <v>1.431811348748618</v>
+        <v>1.797514346716798</v>
       </c>
       <c r="H22" t="n">
         <v>-0.5</v>
@@ -2110,228 +2320,258 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>25</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>(200, 14)</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>(208, 54)</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O22" t="n">
-        <v>3.948918716265807</v>
-      </c>
-      <c r="P22" t="n">
-        <v>87</v>
-      </c>
       <c r="Q22" t="n">
+        <v>6.723277597539274</v>
+      </c>
+      <c r="R22" t="n">
+        <v>92</v>
+      </c>
+      <c r="S22" t="n">
+        <v>52</v>
+      </c>
+      <c r="T22" t="n">
+        <v>64</v>
+      </c>
+      <c r="U22" t="n">
+        <v>95</v>
+      </c>
+      <c r="V22" t="n">
         <v>50</v>
       </c>
-      <c r="R22" t="n">
+      <c r="W22" t="n">
         <v>63</v>
       </c>
-      <c r="S22" t="n">
-        <v>88</v>
-      </c>
-      <c r="T22" t="n">
-        <v>39</v>
-      </c>
-      <c r="U22" t="n">
-        <v>73</v>
-      </c>
-      <c r="V22" t="n">
-        <v>112</v>
-      </c>
-      <c r="W22" t="n">
-        <v>56.00000000000001</v>
+      <c r="X22" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B23" t="n">
-        <v>1.889805127792641</v>
+        <v>4.984669181836748</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2781522727482825</v>
+        <v>0.4937265401952036</v>
       </c>
       <c r="D23" t="n">
-        <v>1.304445243154095</v>
+        <v>1.307035749575991</v>
       </c>
       <c r="E23" t="n">
-        <v>1.100441164036223</v>
+        <v>0.9136630887730073</v>
       </c>
       <c r="F23" t="n">
-        <v>220.0882328072447</v>
+        <v>331.0684603179762</v>
       </c>
       <c r="G23" t="n">
-        <v>1.100441164036223</v>
+        <v>1.59167528999027</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>(200, 41)</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>(208, 61)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O23" t="n">
-        <v>4.95625443992716</v>
-      </c>
-      <c r="P23" t="n">
-        <v>87</v>
-      </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>2.223799331024363</v>
       </c>
       <c r="R23" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S23" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="T23" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="U23" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="V23" t="n">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="W23" t="n">
-        <v>54.50000000000001</v>
+        <v>76</v>
+      </c>
+      <c r="X23" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>179</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7939091177378828</v>
+        <v>6.355520588655511</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.08810175991447394</v>
+        <v>1.345535888818906</v>
       </c>
       <c r="D24" t="n">
-        <v>2.460451678802926</v>
+        <v>2.190498380248221</v>
       </c>
       <c r="E24" t="n">
-        <v>1.036821239284668</v>
+        <v>1.999387522390191</v>
       </c>
       <c r="F24" t="n">
-        <v>207.3642478569337</v>
+        <v>314.3051065799064</v>
       </c>
       <c r="G24" t="n">
-        <v>1.036821239284668</v>
+        <v>1.511082243172627</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>(200, 7)</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>(208, 34)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O24" t="n">
-        <v>12.76845094003999</v>
-      </c>
-      <c r="P24" t="n">
-        <v>87</v>
-      </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>0.123033770952803</v>
       </c>
       <c r="R24" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S24" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="T24" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="U24" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="V24" t="n">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="W24" t="n">
-        <v>55.50000000000001</v>
+        <v>61</v>
+      </c>
+      <c r="X24" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>54.80769230769231</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>322</v>
+        <v>620</v>
       </c>
       <c r="B25" t="n">
-        <v>1.452604573329204</v>
+        <v>6.294154716679206</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.06683225434772226</v>
+        <v>0.9297494008820576</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1911496335893197</v>
+        <v>3.568868098121158</v>
       </c>
       <c r="E25" t="n">
-        <v>1.033409254517001</v>
+        <v>1.76496706552419</v>
       </c>
       <c r="F25" t="n">
-        <v>206.6818509034003</v>
+        <v>311.1395468275554</v>
       </c>
       <c r="G25" t="n">
-        <v>1.033409254517001</v>
+        <v>1.495863205901709</v>
       </c>
       <c r="H25" t="n">
         <v>-0.5</v>
@@ -2341,151 +2581,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>25</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>(200, 37)</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>16.46273224811877</v>
-      </c>
-      <c r="P25" t="n">
-        <v>87</v>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>0.6088885935097956</v>
       </c>
       <c r="R25" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S25" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="T25" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="U25" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="V25" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="W25" t="n">
-        <v>54</v>
+        <v>74</v>
+      </c>
+      <c r="X25" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1902989327228858</v>
+        <v>1.879908616271236</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.5449004283830385</v>
+        <v>-0.3042329568540259</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1379490792374229</v>
+        <v>1.282906524898564</v>
       </c>
       <c r="E26" t="n">
-        <v>1.022373494923279</v>
+        <v>1.172018521454829</v>
       </c>
       <c r="F26" t="n">
-        <v>204.4746989846559</v>
+        <v>310.8185747958196</v>
       </c>
       <c r="G26" t="n">
-        <v>1.022373494923279</v>
+        <v>1.494320071133748</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>20</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>(200, 76)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>2.876257462225007</v>
-      </c>
-      <c r="P26" t="n">
-        <v>87</v>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>(208, 41)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>5.911762639347249</v>
       </c>
       <c r="R26" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S26" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="T26" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="U26" t="n">
+        <v>103</v>
+      </c>
+      <c r="V26" t="n">
         <v>46</v>
       </c>
-      <c r="V26" t="n">
-        <v>104</v>
-      </c>
       <c r="W26" t="n">
-        <v>52</v>
+        <v>59</v>
+      </c>
+      <c r="X26" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>54.80769230769231</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="B27" t="n">
-        <v>3.714543576103685</v>
+        <v>0.24722631610208</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6295005609120105</v>
+        <v>-0.5700406115512539</v>
       </c>
       <c r="D27" t="n">
-        <v>1.260417273463561</v>
+        <v>0.2266275212219612</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9798016061671384</v>
+        <v>0.5088409644745401</v>
       </c>
       <c r="F27" t="n">
-        <v>195.9603212334277</v>
+        <v>291.2464562816534</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9798016061671384</v>
+        <v>1.400223347507949</v>
       </c>
       <c r="H27" t="n">
         <v>-0.5</v>
@@ -2495,51 +2755,61 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>20</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>(200, 61)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>(208, 52)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O27" t="n">
-        <v>0.5564745561904144</v>
-      </c>
-      <c r="P27" t="n">
-        <v>87</v>
-      </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>3.456357177250083</v>
       </c>
       <c r="R27" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S27" t="n">
+        <v>52</v>
+      </c>
+      <c r="T27" t="n">
+        <v>64</v>
+      </c>
+      <c r="U27" t="n">
         <v>84</v>
       </c>
-      <c r="T27" t="n">
-        <v>42</v>
-      </c>
-      <c r="U27" t="n">
-        <v>74</v>
-      </c>
       <c r="V27" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="W27" t="n">
-        <v>55.00000000000001</v>
+        <v>65</v>
+      </c>
+      <c r="X27" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="28">
@@ -2547,22 +2817,22 @@
         <v>210</v>
       </c>
       <c r="B28" t="n">
-        <v>2.412932149652866</v>
+        <v>1.478848192666362</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2170397021050753</v>
+        <v>-0.3042181024672443</v>
       </c>
       <c r="D28" t="n">
-        <v>1.57710708923329</v>
+        <v>1.220829241320182</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9675291471570913</v>
+        <v>1.095833242763158</v>
       </c>
       <c r="F28" t="n">
-        <v>193.5058294314182</v>
+        <v>276.7737193877117</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9675291471570913</v>
+        <v>1.330642881671691</v>
       </c>
       <c r="H28" t="n">
         <v>-0.5</v>
@@ -2572,128 +2842,148 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>25</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>(200, 10)</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>(208, 10)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O28" t="n">
-        <v>5.457844061584097</v>
-      </c>
-      <c r="P28" t="n">
-        <v>87</v>
-      </c>
       <c r="Q28" t="n">
+        <v>5.373976666345696</v>
+      </c>
+      <c r="R28" t="n">
+        <v>92</v>
+      </c>
+      <c r="S28" t="n">
+        <v>52</v>
+      </c>
+      <c r="T28" t="n">
+        <v>64</v>
+      </c>
+      <c r="U28" t="n">
+        <v>112</v>
+      </c>
+      <c r="V28" t="n">
+        <v>46</v>
+      </c>
+      <c r="W28" t="n">
         <v>50</v>
       </c>
-      <c r="R28" t="n">
-        <v>63</v>
-      </c>
-      <c r="S28" t="n">
-        <v>106</v>
-      </c>
-      <c r="T28" t="n">
-        <v>44</v>
-      </c>
-      <c r="U28" t="n">
-        <v>50</v>
-      </c>
-      <c r="V28" t="n">
-        <v>111</v>
-      </c>
-      <c r="W28" t="n">
-        <v>55.50000000000001</v>
+      <c r="X28" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>344</v>
+        <v>640</v>
       </c>
       <c r="B29" t="n">
-        <v>4.259423874038848</v>
+        <v>5.955892567317628</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3518063001486468</v>
+        <v>1.213099704526672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.250856045575465</v>
+        <v>2.819666424870328</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9625293473269335</v>
+        <v>0.6821789209327914</v>
       </c>
       <c r="F29" t="n">
-        <v>192.5058694653867</v>
+        <v>254.9162179769857</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9625293473269335</v>
+        <v>1.22555874027397</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>(200, 54)</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>(208, 63)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O29" t="n">
-        <v>1.73596392935613</v>
-      </c>
-      <c r="P29" t="n">
-        <v>87</v>
-      </c>
       <c r="Q29" t="n">
+        <v>0.01027041363608219</v>
+      </c>
+      <c r="R29" t="n">
+        <v>92</v>
+      </c>
+      <c r="S29" t="n">
+        <v>52</v>
+      </c>
+      <c r="T29" t="n">
+        <v>64</v>
+      </c>
+      <c r="U29" t="n">
+        <v>102</v>
+      </c>
+      <c r="V29" t="n">
         <v>50</v>
       </c>
-      <c r="R29" t="n">
-        <v>63</v>
-      </c>
-      <c r="S29" t="n">
-        <v>91</v>
-      </c>
-      <c r="T29" t="n">
-        <v>46</v>
-      </c>
-      <c r="U29" t="n">
-        <v>63</v>
-      </c>
-      <c r="V29" t="n">
-        <v>110</v>
-      </c>
       <c r="W29" t="n">
-        <v>55.00000000000001</v>
+        <v>56</v>
+      </c>
+      <c r="X29" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>55.28846153846154</v>
       </c>
     </row>
     <row r="30">
@@ -2701,22 +2991,22 @@
         <v>368</v>
       </c>
       <c r="B30" t="n">
-        <v>2.564075066862043</v>
+        <v>2.623862172183033</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2613777178796526</v>
+        <v>0.2246314411782546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7839881341478745</v>
+        <v>0.8795321913034185</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8803296924751777</v>
+        <v>1.039604123545392</v>
       </c>
       <c r="F30" t="n">
-        <v>176.0659384950355</v>
+        <v>251.0375146395648</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8803296924751777</v>
+        <v>1.206911128074831</v>
       </c>
       <c r="H30" t="n">
         <v>-0.5</v>
@@ -2726,151 +3016,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>25</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>(200, 52)</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>(208, 52)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>XGBClassifier</t>
         </is>
       </c>
-      <c r="O30" t="n">
-        <v>2.368036493763069</v>
-      </c>
-      <c r="P30" t="n">
-        <v>87</v>
-      </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>4.372850397719237</v>
       </c>
       <c r="R30" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S30" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="T30" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U30" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="V30" t="n">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="W30" t="n">
-        <v>54</v>
+        <v>65</v>
+      </c>
+      <c r="X30" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="B31" t="n">
-        <v>1.398132204141912</v>
+        <v>-0.8537446715196952</v>
       </c>
       <c r="C31" t="n">
-        <v>0.658717011952576</v>
+        <v>-0.4613403407338538</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7637971588794388</v>
+        <v>0.2059704428497753</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7143484483183258</v>
+        <v>0.3987459067485791</v>
       </c>
       <c r="F31" t="n">
-        <v>142.8696896636652</v>
+        <v>247.4872546430348</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7143484483183258</v>
+        <v>1.189842570399206</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>20</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>(200, 20)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>0.08445422746992133</v>
-      </c>
-      <c r="P31" t="n">
-        <v>87</v>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>(208, 39)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>50</v>
+        <v>3.579099344545773</v>
       </c>
       <c r="R31" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S31" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="T31" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U31" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="V31" t="n">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="W31" t="n">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="X31" t="n">
+        <v>112</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>518</v>
+        <v>323</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.03447997891877207</v>
+        <v>2.309532088204892</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2647896570979749</v>
+        <v>-0.2230366389173398</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7092173212101145</v>
+        <v>0.8692539446071667</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7082957944465974</v>
+        <v>1.489417732686686</v>
       </c>
       <c r="F32" t="n">
-        <v>141.6591588893195</v>
+        <v>240.1144309231131</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7082957944465974</v>
+        <v>1.154396302514967</v>
       </c>
       <c r="H32" t="n">
         <v>-0.5</v>
@@ -2880,151 +3190,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>(200, 77)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>1.674937541780647</v>
-      </c>
-      <c r="P32" t="n">
-        <v>87</v>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>(208, 19)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>50</v>
+        <v>6.175814646950453</v>
       </c>
       <c r="R32" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S32" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="T32" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="U32" t="n">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="V32" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="W32" t="n">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="X32" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>56.73076923076923</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>207</v>
+        <v>322</v>
       </c>
       <c r="B33" t="n">
-        <v>2.378671009487927</v>
+        <v>1.528913982986759</v>
       </c>
       <c r="C33" t="n">
-        <v>0.624466922386664</v>
+        <v>-0.1163904446161338</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4958183655044697</v>
+        <v>-0.2110456796923216</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6654097481816978</v>
+        <v>1.034747288815171</v>
       </c>
       <c r="F33" t="n">
-        <v>133.0819496363396</v>
+        <v>239.1566120910574</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6654097481816978</v>
+        <v>1.14979140428393</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>(200, 30)</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>0.06556444277072922</v>
-      </c>
-      <c r="P33" t="n">
-        <v>87</v>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>(208, 37)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q33" t="n">
-        <v>50</v>
+        <v>10.87874398174219</v>
       </c>
       <c r="R33" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S33" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="T33" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="U33" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="V33" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="W33" t="n">
-        <v>54</v>
+        <v>68</v>
+      </c>
+      <c r="X33" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>380</v>
+        <v>179</v>
       </c>
       <c r="B34" t="n">
-        <v>1.106462902089342</v>
+        <v>0.8528217800394219</v>
       </c>
       <c r="C34" t="n">
-        <v>0.107076280725166</v>
+        <v>-0.132757841071226</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1943324379530064</v>
+        <v>2.484471687964467</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6112716460258446</v>
+        <v>0.9659109027274647</v>
       </c>
       <c r="F34" t="n">
-        <v>122.2543292051689</v>
+        <v>236.1863146269246</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6112716460258446</v>
+        <v>1.135511128014061</v>
       </c>
       <c r="H34" t="n">
         <v>-0.25</v>
@@ -3034,51 +3364,61 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>(200, 19)</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>(208, 7)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O34" t="n">
-        <v>4.708749331654532</v>
-      </c>
-      <c r="P34" t="n">
-        <v>87</v>
-      </c>
       <c r="Q34" t="n">
-        <v>50</v>
+        <v>9.553250933064257</v>
       </c>
       <c r="R34" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S34" t="n">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="T34" t="n">
+        <v>64</v>
+      </c>
+      <c r="U34" t="n">
+        <v>104</v>
+      </c>
+      <c r="V34" t="n">
         <v>37</v>
       </c>
-      <c r="U34" t="n">
-        <v>54</v>
-      </c>
-      <c r="V34" t="n">
-        <v>108</v>
-      </c>
       <c r="W34" t="n">
-        <v>54</v>
+        <v>67</v>
+      </c>
+      <c r="X34" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>55.76923076923077</v>
       </c>
     </row>
     <row r="35">
@@ -3086,22 +3426,22 @@
         <v>295</v>
       </c>
       <c r="B35" t="n">
-        <v>3.891413859760703</v>
+        <v>3.983351654248472</v>
       </c>
       <c r="C35" t="n">
-        <v>0.560585513794955</v>
+        <v>0.5632488475787736</v>
       </c>
       <c r="D35" t="n">
-        <v>1.051037103029643</v>
+        <v>1.036252346171836</v>
       </c>
       <c r="E35" t="n">
-        <v>0.608950896749721</v>
+        <v>0.6029944678396553</v>
       </c>
       <c r="F35" t="n">
-        <v>121.7901793499442</v>
+        <v>216.7787963025432</v>
       </c>
       <c r="G35" t="n">
-        <v>0.608950896749721</v>
+        <v>1.042205751454535</v>
       </c>
       <c r="H35" t="n">
         <v>-0.5</v>
@@ -3111,74 +3451,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>(200, 40)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>(208, 40)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O35" t="n">
-        <v>0.0862765479388691</v>
-      </c>
-      <c r="P35" t="n">
-        <v>87</v>
-      </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>0.8503468865220828</v>
       </c>
       <c r="R35" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S35" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="T35" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="U35" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="V35" t="n">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="W35" t="n">
-        <v>54.50000000000001</v>
+        <v>74</v>
+      </c>
+      <c r="X35" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>55.28846153846154</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>636</v>
+        <v>277</v>
       </c>
       <c r="B36" t="n">
-        <v>1.784685015293205</v>
+        <v>2.645811809886506</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0007434173485513895</v>
+        <v>-0.07671524990123785</v>
       </c>
       <c r="D36" t="n">
-        <v>1.187747282158764</v>
+        <v>1.015427274493863</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6051323887351594</v>
+        <v>0.4716162657978687</v>
       </c>
       <c r="F36" t="n">
-        <v>121.0264777470319</v>
+        <v>211.500279165312</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6051323887351594</v>
+        <v>1.016828265217846</v>
       </c>
       <c r="H36" t="n">
         <v>-0.5</v>
@@ -3188,74 +3538,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>20</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>(200, 19)</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>(208, 72)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O36" t="n">
-        <v>814.9874458328289</v>
-      </c>
-      <c r="P36" t="n">
-        <v>87</v>
-      </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>14.25457802101794</v>
       </c>
       <c r="R36" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S36" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="T36" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="U36" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="V36" t="n">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="W36" t="n">
-        <v>56.00000000000001</v>
+        <v>79</v>
+      </c>
+      <c r="X36" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>55.28846153846154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="B37" t="n">
-        <v>3.462943192050653</v>
+        <v>1.534419901420799</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1038625514229634</v>
+        <v>0.7219960288800493</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6184927272920901</v>
+        <v>0.8791905763626157</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5934730957046876</v>
+        <v>0.7776713533245723</v>
       </c>
       <c r="F37" t="n">
-        <v>118.6946191409375</v>
+        <v>177.5826015824306</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5934730957046876</v>
+        <v>0.8537625076078393</v>
       </c>
       <c r="H37" t="n">
         <v>-0.25</v>
@@ -3265,151 +3625,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>(200, 55)</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>(208, 20)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O37" t="n">
-        <v>6.714023847612454</v>
-      </c>
-      <c r="P37" t="n">
-        <v>87</v>
-      </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>0.182503051896538</v>
       </c>
       <c r="R37" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S37" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="T37" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="U37" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="V37" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="W37" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="X37" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="B38" t="n">
-        <v>0.382958060739507</v>
+        <v>2.420408143826572</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4518910228385338</v>
+        <v>0.6187114297522541</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3738035053211989</v>
+        <v>0.5780961442547474</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5866625780941552</v>
+        <v>0.7033188553357972</v>
       </c>
       <c r="F38" t="n">
-        <v>117.3325156188311</v>
+        <v>177.4073366795427</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5866625780941552</v>
+        <v>0.8529198878824166</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>20</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>(200, 52)</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>(208, 30)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O38" t="n">
-        <v>2.298239063057858</v>
-      </c>
-      <c r="P38" t="n">
-        <v>87</v>
-      </c>
       <c r="Q38" t="n">
-        <v>50</v>
+        <v>0.3785423169310849</v>
       </c>
       <c r="R38" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S38" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="T38" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="U38" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="V38" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="W38" t="n">
-        <v>53</v>
+        <v>67</v>
+      </c>
+      <c r="X38" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>318</v>
+        <v>636</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.2547401381420477</v>
+        <v>1.950715026543088</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.344997123215921</v>
+        <v>0.03017396392081181</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0634271916532804</v>
+        <v>1.311269390018035</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5514703240338651</v>
+        <v>0.6879939654951249</v>
       </c>
       <c r="F39" t="n">
-        <v>110.294064806773</v>
+        <v>172.534782446267</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5514703240338651</v>
+        <v>0.8294941463762837</v>
       </c>
       <c r="H39" t="n">
         <v>-0.5</v>
@@ -3419,74 +3799,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>15</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>(200, 73)</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>2.598478036260958</v>
-      </c>
-      <c r="P39" t="n">
-        <v>87</v>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>(208, 19)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>26.49039365703486</v>
       </c>
       <c r="R39" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S39" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="T39" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="U39" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="V39" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="W39" t="n">
-        <v>50.5</v>
+        <v>53</v>
+      </c>
+      <c r="X39" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>56.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>326</v>
+        <v>591</v>
       </c>
       <c r="B40" t="n">
-        <v>1.504526725191379</v>
+        <v>0.9748859921999633</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3065247676723519</v>
+        <v>0.5493779679843243</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8803771404414372</v>
+        <v>0.3694258028053627</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5390317710184598</v>
+        <v>0.455875046902125</v>
       </c>
       <c r="F40" t="n">
-        <v>107.806354203692</v>
+        <v>168.7476540851955</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5390317710184598</v>
+        <v>0.8112867984865169</v>
       </c>
       <c r="H40" t="n">
         <v>-0.25</v>
@@ -3496,613 +3886,693 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>20</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>(200, 82)</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>0.7585259915917706</v>
-      </c>
-      <c r="P40" t="n">
-        <v>87</v>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>(208, 35)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q40" t="n">
-        <v>50</v>
+        <v>0.4767370476525294</v>
       </c>
       <c r="R40" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S40" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="T40" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="U40" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="V40" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="W40" t="n">
-        <v>50</v>
+        <v>56</v>
+      </c>
+      <c r="X40" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>52.88461538461539</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="B41" t="n">
-        <v>2.260306942394478</v>
+        <v>3.476735986139433</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1068437782589247</v>
+        <v>-0.1357956034146925</v>
       </c>
       <c r="D41" t="n">
-        <v>1.007552835293966</v>
+        <v>0.5686717441022328</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5193370740461911</v>
+        <v>0.6211784539984581</v>
       </c>
       <c r="F41" t="n">
-        <v>103.8674148092382</v>
+        <v>163.207801620975</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5193370740461911</v>
+        <v>0.7846528924085339</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>(200, 72)</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>(208, 55)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O41" t="n">
-        <v>3.860714236327661</v>
-      </c>
-      <c r="P41" t="n">
-        <v>87</v>
-      </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>6.778190697473184</v>
       </c>
       <c r="R41" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S41" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="T41" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="U41" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="V41" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="W41" t="n">
-        <v>54.50000000000001</v>
+        <v>68</v>
+      </c>
+      <c r="X41" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>438</v>
+        <v>165</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.3029593478277892</v>
+        <v>0.5479184307154751</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1672654410770363</v>
+        <v>-0.2164144545470545</v>
       </c>
       <c r="D42" t="n">
-        <v>1.302038518743271</v>
+        <v>0.3542284452962013</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5130442687622977</v>
+        <v>1.1448457359234</v>
       </c>
       <c r="F42" t="n">
-        <v>102.6088537524595</v>
+        <v>161.4643494575965</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5130442687622977</v>
+        <v>0.7762709108538295</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>15</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>(200, 40)</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>(208, 76)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>XGBClassifier</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>2.067246081789294</v>
-      </c>
-      <c r="P42" t="n">
-        <v>87</v>
-      </c>
       <c r="Q42" t="n">
-        <v>50</v>
+        <v>4.586964246350961</v>
       </c>
       <c r="R42" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S42" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="T42" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="U42" t="n">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="V42" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="W42" t="n">
-        <v>51.5</v>
+        <v>47</v>
+      </c>
+      <c r="X42" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>51.92307692307693</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>343</v>
+        <v>231</v>
       </c>
       <c r="B43" t="n">
-        <v>2.528256462489965</v>
+        <v>-0.4610482683514229</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3173498276967362</v>
+        <v>0.5562253138381993</v>
       </c>
       <c r="D43" t="n">
-        <v>1.244685167053156</v>
+        <v>0.6389413392953469</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4327801402619758</v>
+        <v>0.3315703490378328</v>
       </c>
       <c r="F43" t="n">
-        <v>86.55602805239516</v>
+        <v>152.8576433209222</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4327801402619758</v>
+        <v>0.7348925159659719</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>20</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>(200, 54)</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>0.3637320788954276</v>
-      </c>
-      <c r="P43" t="n">
-        <v>87</v>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>(208, 29)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q43" t="n">
-        <v>50</v>
+        <v>0.3212137198411384</v>
       </c>
       <c r="R43" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S43" t="n">
+        <v>52</v>
+      </c>
+      <c r="T43" t="n">
+        <v>64</v>
+      </c>
+      <c r="U43" t="n">
         <v>82</v>
       </c>
-      <c r="T43" t="n">
-        <v>58</v>
-      </c>
-      <c r="U43" t="n">
-        <v>60</v>
-      </c>
       <c r="V43" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="W43" t="n">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="X43" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>50.48076923076923</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>229</v>
+        <v>279</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.7084693814019232</v>
+        <v>2.844667158088734</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.3247901652988194</v>
+        <v>0.1262881762948791</v>
       </c>
       <c r="D44" t="n">
-        <v>0.24141738712222</v>
+        <v>1.363248437508651</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4150859195310157</v>
+        <v>0.3035608181367851</v>
       </c>
       <c r="F44" t="n">
-        <v>83.01718390620314</v>
+        <v>134.4392155876429</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4150859195310157</v>
+        <v>0.6463423826328984</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>20</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="b">
         <v>0</v>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>(200, 39)</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>2.278012587447409</v>
-      </c>
-      <c r="P44" t="n">
-        <v>87</v>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>(208, 54)</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>4.117996011944208</v>
       </c>
       <c r="R44" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S44" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="T44" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U44" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="V44" t="n">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="W44" t="n">
-        <v>52.5</v>
+        <v>68</v>
+      </c>
+      <c r="X44" t="n">
+        <v>112</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>305</v>
+        <v>438</v>
       </c>
       <c r="B45" t="n">
-        <v>2.520223813849437</v>
+        <v>-0.2928397983429732</v>
       </c>
       <c r="C45" t="n">
-        <v>0.269357060982063</v>
+        <v>0.1638323303482211</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8943001665801273</v>
+        <v>1.323324174791349</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3775193245213183</v>
+        <v>0.5266917492585272</v>
       </c>
       <c r="F45" t="n">
-        <v>75.50386490426365</v>
+        <v>125.6275387537833</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3775193245213183</v>
+        <v>0.6039785517008811</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>(200, 35)</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>0.4015571863789307</v>
-      </c>
-      <c r="P45" t="n">
-        <v>87</v>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>(208, 40)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>2.686565102364969</v>
       </c>
       <c r="R45" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S45" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="T45" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="U45" t="n">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="V45" t="n">
+        <v>37</v>
+      </c>
+      <c r="W45" t="n">
+        <v>67</v>
+      </c>
+      <c r="X45" t="n">
         <v>108</v>
       </c>
-      <c r="W45" t="n">
-        <v>54</v>
+      <c r="Y45" t="n">
+        <v>51.92307692307693</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>392</v>
+        <v>630</v>
       </c>
       <c r="B46" t="n">
-        <v>0.8702675175384303</v>
+        <v>0.3656127187905724</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3088591169248784</v>
+        <v>-0.01068501359638645</v>
       </c>
       <c r="D46" t="n">
-        <v>1.052388385063452</v>
+        <v>1.296581783919058</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3721309718345975</v>
+        <v>0.3436740676867479</v>
       </c>
       <c r="F46" t="n">
-        <v>74.4261943669195</v>
+        <v>125.2327236785703</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3721309718345975</v>
+        <v>0.6020804023008187</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J46" t="n">
-        <v>15</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>(200, 31)</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>0.2048566852734616</v>
-      </c>
-      <c r="P46" t="n">
-        <v>87</v>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>(208, 74)</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>57.34811756387798</v>
       </c>
       <c r="R46" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S46" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="T46" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="U46" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="V46" t="n">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="W46" t="n">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="X46" t="n">
+        <v>112</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="B47" t="n">
-        <v>2.166406422162155</v>
+        <v>1.937897462766804</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2106375906668923</v>
+        <v>0.02888900524444978</v>
       </c>
       <c r="D47" t="n">
-        <v>1.172119723266623</v>
+        <v>0.4829553193793441</v>
       </c>
       <c r="E47" t="n">
-        <v>0.360355461460026</v>
+        <v>0.5312623032289051</v>
       </c>
       <c r="F47" t="n">
-        <v>72.0710922920052</v>
+        <v>125.2099023625982</v>
       </c>
       <c r="G47" t="n">
-        <v>0.360355461460026</v>
+        <v>0.6019706844355681</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>15</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="b">
         <v>0</v>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>(200, 54)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>0.710784197251389</v>
-      </c>
-      <c r="P47" t="n">
-        <v>87</v>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>(208, 82)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>19.83736284243363</v>
       </c>
       <c r="R47" t="n">
+        <v>92</v>
+      </c>
+      <c r="S47" t="n">
+        <v>52</v>
+      </c>
+      <c r="T47" t="n">
+        <v>64</v>
+      </c>
+      <c r="U47" t="n">
+        <v>83</v>
+      </c>
+      <c r="V47" t="n">
         <v>63</v>
       </c>
-      <c r="S47" t="n">
-        <v>81</v>
-      </c>
-      <c r="T47" t="n">
-        <v>51</v>
-      </c>
-      <c r="U47" t="n">
-        <v>68</v>
-      </c>
-      <c r="V47" t="n">
-        <v>106</v>
-      </c>
       <c r="W47" t="n">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="X47" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>52.88461538461539</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3867011384490525</v>
+        <v>2.452298469981855</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01975754625821395</v>
+        <v>-0.4990975001367948</v>
       </c>
       <c r="D48" t="n">
-        <v>1.319400651470644</v>
+        <v>0.9965692234594692</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3454991594492177</v>
+        <v>0.2832515743388083</v>
       </c>
       <c r="F48" t="n">
-        <v>69.09983188984353</v>
+        <v>122.8453703325532</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3454991594492177</v>
+        <v>0.5906027419834289</v>
       </c>
       <c r="H48" t="n">
         <v>-0.5</v>
@@ -4112,305 +4582,345 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J48" t="n">
-        <v>15</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="b">
         <v>0</v>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>(200, 74)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>16.48694675613277</v>
-      </c>
-      <c r="P48" t="n">
-        <v>87</v>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>2.183341414896997</v>
       </c>
       <c r="R48" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S48" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="T48" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="U48" t="n">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="V48" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="W48" t="n">
-        <v>53</v>
+        <v>82</v>
+      </c>
+      <c r="X48" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>644</v>
+        <v>96</v>
       </c>
       <c r="B49" t="n">
-        <v>1.728902898980987</v>
+        <v>1.672314832737417</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.3466632764776548</v>
+        <v>0.4956162802497022</v>
       </c>
       <c r="D49" t="n">
-        <v>0.795807619488773</v>
+        <v>0.1781378227089387</v>
       </c>
       <c r="E49" t="n">
-        <v>0.319700821761437</v>
+        <v>0.4947302925457389</v>
       </c>
       <c r="F49" t="n">
-        <v>63.94016435228741</v>
+        <v>122.4287826193221</v>
       </c>
       <c r="G49" t="n">
-        <v>0.319700821761437</v>
+        <v>0.5885999164390484</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="b">
         <v>0</v>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="M49" t="n">
+        <v>4</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O49" t="n">
-        <v>1.922222927706172</v>
-      </c>
-      <c r="P49" t="n">
-        <v>87</v>
-      </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>0.1876121505582889</v>
       </c>
       <c r="R49" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S49" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="T49" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="U49" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="V49" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="W49" t="n">
-        <v>53.5</v>
+        <v>49</v>
+      </c>
+      <c r="X49" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>52.40384615384615</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.3001861750092815</v>
+        <v>2.736764396668946</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4100241547179065</v>
+        <v>0.2740869806417578</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.04952228565332632</v>
+        <v>1.248398609306711</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2433544073827348</v>
+        <v>0.406749094740983</v>
       </c>
       <c r="F50" t="n">
-        <v>48.67088147654695</v>
+        <v>111.003208940191</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2433544073827348</v>
+        <v>0.5336692737509184</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="b">
         <v>0</v>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>(200, 21)</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>1.59351236892412</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>(208, 54)</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.9470799835197012</v>
+      </c>
+      <c r="R50" t="n">
+        <v>92</v>
+      </c>
+      <c r="S50" t="n">
+        <v>52</v>
+      </c>
+      <c r="T50" t="n">
+        <v>64</v>
+      </c>
+      <c r="U50" t="n">
         <v>87</v>
       </c>
-      <c r="Q50" t="n">
-        <v>50</v>
-      </c>
-      <c r="R50" t="n">
-        <v>63</v>
-      </c>
-      <c r="S50" t="n">
-        <v>71</v>
-      </c>
-      <c r="T50" t="n">
-        <v>67</v>
-      </c>
-      <c r="U50" t="n">
-        <v>62</v>
-      </c>
       <c r="V50" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="W50" t="n">
-        <v>48.5</v>
+        <v>61</v>
+      </c>
+      <c r="X50" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>53.36538461538461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="B51" t="n">
-        <v>1.63751826344646</v>
+        <v>3.23016861950147</v>
       </c>
       <c r="C51" t="n">
-        <v>0.02320050885889273</v>
+        <v>0.2083985188366422</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1840560810789917</v>
+        <v>1.070368958782617</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2347031127727016</v>
+        <v>0.3838408368485255</v>
       </c>
       <c r="F51" t="n">
-        <v>46.94062255454031</v>
+        <v>108.3052816786075</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2347031127727016</v>
+        <v>0.5206984696086899</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J51" t="n">
-        <v>15</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="b">
         <v>0</v>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>(200, 82)</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>(208, 35)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O51" t="n">
-        <v>9.116291595162153</v>
-      </c>
-      <c r="P51" t="n">
-        <v>87</v>
-      </c>
       <c r="Q51" t="n">
-        <v>50</v>
+        <v>1.498570875241445</v>
       </c>
       <c r="R51" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S51" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="T51" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="U51" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="V51" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="W51" t="n">
-        <v>52.5</v>
+        <v>64</v>
+      </c>
+      <c r="X51" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>54.32692307692307</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>664</v>
+        <v>380</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.1871869141582019</v>
+        <v>0.9271561379772471</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2576773553483338</v>
+        <v>0.05555602359247118</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1479455428013055</v>
+        <v>0.1365006518083226</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2002198652203508</v>
+        <v>0.5885347442871195</v>
       </c>
       <c r="F52" t="n">
-        <v>40.04397304407016</v>
+        <v>106.815222729109</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2002198652203508</v>
+        <v>0.5135347246591777</v>
       </c>
       <c r="H52" t="n">
         <v>-0.25</v>
@@ -4420,74 +4930,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v>10</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>(200, 58)</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>1.777017696994326</v>
-      </c>
-      <c r="P52" t="n">
-        <v>87</v>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>(208, 19)</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
       </c>
       <c r="Q52" t="n">
-        <v>50</v>
+        <v>8.243547170081674</v>
       </c>
       <c r="R52" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="S52" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="T52" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="U52" t="n">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="V52" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="W52" t="n">
-        <v>47</v>
+        <v>55</v>
+      </c>
+      <c r="X52" t="n">
+        <v>112</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>163</v>
+        <v>392</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9352149667358708</v>
+        <v>0.9185138575248493</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1634604763142185</v>
+        <v>0.321880437868301</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1477492002039915</v>
+        <v>1.137698095972243</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1714779866563274</v>
+        <v>0.4206835611511419</v>
       </c>
       <c r="F53" t="n">
-        <v>34.29559733126547</v>
+        <v>106.2348126850542</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1714779866563274</v>
+        <v>0.5107442917550681</v>
       </c>
       <c r="H53" t="n">
         <v>-0.25</v>
@@ -4497,51 +5017,844 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J53" t="n">
-        <v>10</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="b">
         <v>0</v>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>(200, 18)</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>(208, 31)</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.5867515750181803</v>
+      </c>
+      <c r="R53" t="n">
+        <v>92</v>
+      </c>
+      <c r="S53" t="n">
+        <v>52</v>
+      </c>
+      <c r="T53" t="n">
+        <v>64</v>
+      </c>
+      <c r="U53" t="n">
+        <v>85</v>
+      </c>
+      <c r="V53" t="n">
+        <v>38</v>
+      </c>
+      <c r="W53" t="n">
+        <v>85</v>
+      </c>
+      <c r="X53" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>51.44230769230769</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2.92749933395027</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0008701192591919948</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1712051609116896</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.1854250158005037</v>
+      </c>
+      <c r="F54" t="n">
+        <v>105.8718259381049</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.508999163163966</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>(208, 36)</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O53" t="n">
-        <v>0.04904861727367611</v>
-      </c>
-      <c r="P53" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q53" t="n">
+      <c r="Q54" t="n">
+        <v>585.9763211041092</v>
+      </c>
+      <c r="R54" t="n">
+        <v>92</v>
+      </c>
+      <c r="S54" t="n">
+        <v>52</v>
+      </c>
+      <c r="T54" t="n">
+        <v>64</v>
+      </c>
+      <c r="U54" t="n">
+        <v>81</v>
+      </c>
+      <c r="V54" t="n">
         <v>50</v>
       </c>
-      <c r="R53" t="n">
+      <c r="W54" t="n">
+        <v>77</v>
+      </c>
+      <c r="X54" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>51.92307692307693</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1.575736721039041</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.3543074910178515</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.6155804288622111</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.2769893913442598</v>
+      </c>
+      <c r="F55" t="n">
+        <v>101.2783070748654</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.4869149378599297</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>(208, 35)</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.3742722076271226</v>
+      </c>
+      <c r="R55" t="n">
+        <v>92</v>
+      </c>
+      <c r="S55" t="n">
+        <v>52</v>
+      </c>
+      <c r="T55" t="n">
+        <v>64</v>
+      </c>
+      <c r="U55" t="n">
+        <v>78</v>
+      </c>
+      <c r="V55" t="n">
+        <v>47</v>
+      </c>
+      <c r="W55" t="n">
+        <v>83</v>
+      </c>
+      <c r="X55" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>52.40384615384615</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1.924564570991146</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.4283130950481069</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2466287044366527</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3974506123881617</v>
+      </c>
+      <c r="F56" t="n">
+        <v>100.4779072298223</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.483066861681838</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>(208, 12)</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.1278358454755658</v>
+      </c>
+      <c r="R56" t="n">
+        <v>92</v>
+      </c>
+      <c r="S56" t="n">
+        <v>52</v>
+      </c>
+      <c r="T56" t="n">
+        <v>64</v>
+      </c>
+      <c r="U56" t="n">
+        <v>90</v>
+      </c>
+      <c r="V56" t="n">
+        <v>56</v>
+      </c>
+      <c r="W56" t="n">
+        <v>62</v>
+      </c>
+      <c r="X56" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>51.92307692307693</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>518</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.02252493936966147</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.3077780129975309</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.5821775893230775</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.6653837762316135</v>
+      </c>
+      <c r="F57" t="n">
+        <v>86.56739273619442</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.4161893881547808</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>(208, 77)</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.35223885586044</v>
+      </c>
+      <c r="R57" t="n">
+        <v>92</v>
+      </c>
+      <c r="S57" t="n">
+        <v>52</v>
+      </c>
+      <c r="T57" t="n">
+        <v>64</v>
+      </c>
+      <c r="U57" t="n">
+        <v>106</v>
+      </c>
+      <c r="V57" t="n">
+        <v>45</v>
+      </c>
+      <c r="W57" t="n">
+        <v>57</v>
+      </c>
+      <c r="X57" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>50.48076923076923</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>626</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1.786925214213382</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.2422370340728549</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.4695880751514517</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.1269543590845302</v>
+      </c>
+      <c r="F58" t="n">
+        <v>69.6935061483112</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.3350649334053423</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>(208, 26)</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.3832110134925475</v>
+      </c>
+      <c r="R58" t="n">
+        <v>92</v>
+      </c>
+      <c r="S58" t="n">
+        <v>52</v>
+      </c>
+      <c r="T58" t="n">
+        <v>64</v>
+      </c>
+      <c r="U58" t="n">
+        <v>92</v>
+      </c>
+      <c r="V58" t="n">
+        <v>69</v>
+      </c>
+      <c r="W58" t="n">
+        <v>47</v>
+      </c>
+      <c r="X58" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>52.40384615384615</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2.801281448059903</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.2892413130426206</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.3543852096579261</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1208262704845183</v>
+      </c>
+      <c r="F59" t="n">
+        <v>66.46580198768405</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.3195471249407887</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>(208, 40)</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.1047769130190001</v>
+      </c>
+      <c r="R59" t="n">
+        <v>92</v>
+      </c>
+      <c r="S59" t="n">
+        <v>52</v>
+      </c>
+      <c r="T59" t="n">
+        <v>64</v>
+      </c>
+      <c r="U59" t="n">
+        <v>98</v>
+      </c>
+      <c r="V59" t="n">
+        <v>39</v>
+      </c>
+      <c r="W59" t="n">
+        <v>71</v>
+      </c>
+      <c r="X59" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>53.36538461538461</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.2826789153971984</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.4086873443331286</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.04418293505768228</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2497856897859163</v>
+      </c>
+      <c r="F60" t="n">
+        <v>63.67942297039244</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.3061510719730406</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>(208, 21)</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.749108276089634</v>
+      </c>
+      <c r="R60" t="n">
+        <v>92</v>
+      </c>
+      <c r="S60" t="n">
+        <v>52</v>
+      </c>
+      <c r="T60" t="n">
+        <v>64</v>
+      </c>
+      <c r="U60" t="n">
+        <v>75</v>
+      </c>
+      <c r="V60" t="n">
+        <v>70</v>
+      </c>
+      <c r="W60" t="n">
         <v>63</v>
       </c>
-      <c r="S53" t="n">
-        <v>92</v>
-      </c>
-      <c r="T53" t="n">
-        <v>41</v>
-      </c>
-      <c r="U53" t="n">
-        <v>67</v>
-      </c>
-      <c r="V53" t="n">
-        <v>105</v>
-      </c>
-      <c r="W53" t="n">
-        <v>52.5</v>
+      <c r="X60" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>49.03846153846153</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>664</v>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.1871869141582019</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.2569628430039752</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1536237862877976</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2080631811721682</v>
+      </c>
+      <c r="F61" t="n">
+        <v>59.9299651888586</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.2881248326387433</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>(208, 58)</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.12127041120216</v>
+      </c>
+      <c r="R61" t="n">
+        <v>92</v>
+      </c>
+      <c r="S61" t="n">
+        <v>52</v>
+      </c>
+      <c r="T61" t="n">
+        <v>64</v>
+      </c>
+      <c r="U61" t="n">
+        <v>100</v>
+      </c>
+      <c r="V61" t="n">
+        <v>58</v>
+      </c>
+      <c r="W61" t="n">
+        <v>50</v>
+      </c>
+      <c r="X61" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>47.11538461538461</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.739596630109902</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.1762591903067227</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.2307343207894862</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1723087208324901</v>
+      </c>
+      <c r="F62" t="n">
+        <v>53.70600115764002</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.2582019286425001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>(208, 30)</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.4648990965701272</v>
+      </c>
+      <c r="R62" t="n">
+        <v>92</v>
+      </c>
+      <c r="S62" t="n">
+        <v>52</v>
+      </c>
+      <c r="T62" t="n">
+        <v>64</v>
+      </c>
+      <c r="U62" t="n">
+        <v>102</v>
+      </c>
+      <c r="V62" t="n">
+        <v>37</v>
+      </c>
+      <c r="W62" t="n">
+        <v>69</v>
+      </c>
+      <c r="X62" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>53.36538461538461</v>
       </c>
     </row>
   </sheetData>
